--- a/Result/24-05-25/NASDAQstock_24-05-25period252RS90.xlsx
+++ b/Result/24-05-25/NASDAQstock_24-05-25period252RS90.xlsx
@@ -3,33 +3,52 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16200" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <color rgb="FF008000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -39,12 +58,36 @@
       <color rgb="00008000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA500"/>
+        <bgColor rgb="FFFFA500"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -65,7 +108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -92,6 +135,15 @@
       <left/>
       <right/>
       <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color rgb="00FF0000"/>
       </top>
       <bottom/>
@@ -100,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -111,9 +163,18 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -477,7 +538,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AP134"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -798,7 +859,7 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AJ2" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -827,7 +888,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>DASH</t>
         </is>
@@ -935,7 +996,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr">
+      <c r="AJ3" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -964,7 +1025,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -1070,7 +1131,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr">
+      <c r="AJ4" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -1099,7 +1160,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>GEV</t>
         </is>
@@ -1210,7 +1271,7 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="inlineStr">
+      <c r="AJ5" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -1345,7 +1406,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr">
+      <c r="AJ6" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -1374,7 +1435,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
@@ -1480,7 +1541,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="inlineStr">
+      <c r="AJ7" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -1509,7 +1570,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>CRS</t>
         </is>
@@ -1615,7 +1676,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="inlineStr">
+      <c r="AJ8" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -1750,7 +1811,7 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AJ9" s="2" t="inlineStr">
+      <c r="AJ9" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -1779,7 +1840,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>KEP</t>
         </is>
@@ -1885,7 +1946,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ10" s="3" t="inlineStr">
+      <c r="AJ10" s="11" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
@@ -1914,7 +1975,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
@@ -2020,7 +2081,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ11" s="3" t="inlineStr">
+      <c r="AJ11" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -2049,7 +2110,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
@@ -2111,7 +2172,7 @@
       <c r="U12" t="n">
         <v>2.222222222222222</v>
       </c>
-      <c r="V12" s="5" t="b">
+      <c r="V12" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W12" t="b">
@@ -2155,7 +2216,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ12" s="2" t="inlineStr">
+      <c r="AJ12" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -2290,7 +2351,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ13" s="3" t="inlineStr">
+      <c r="AJ13" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -2425,7 +2486,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ14" s="3" t="inlineStr">
+      <c r="AJ14" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -2454,7 +2515,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
@@ -2516,7 +2577,7 @@
       <c r="U15" t="n">
         <v>2.777777777777778</v>
       </c>
-      <c r="V15" s="5" t="b">
+      <c r="V15" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W15" t="b">
@@ -2560,7 +2621,7 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AJ15" s="2" t="inlineStr">
+      <c r="AJ15" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -2695,7 +2756,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ16" s="2" t="inlineStr">
+      <c r="AJ16" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -2753,7 +2814,7 @@
       <c r="I17" t="n">
         <v>8.75</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="12" t="n">
         <v>2.117489723387361</v>
       </c>
       <c r="K17" t="n">
@@ -2830,7 +2891,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ17" s="3" t="inlineStr">
+      <c r="AJ17" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -2965,7 +3026,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ18" s="3" t="inlineStr">
+      <c r="AJ18" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -2994,7 +3055,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>DUOL</t>
         </is>
@@ -3056,7 +3117,7 @@
       <c r="U19" t="n">
         <v>16.66666666666666</v>
       </c>
-      <c r="V19" s="5" t="b">
+      <c r="V19" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W19" t="b">
@@ -3100,7 +3161,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ19" s="2" t="inlineStr">
+      <c r="AJ19" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -3129,7 +3190,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>AEM</t>
         </is>
@@ -3235,7 +3296,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ20" s="3" t="inlineStr">
+      <c r="AJ20" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -3370,7 +3431,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ21" s="2" t="inlineStr">
+      <c r="AJ21" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -3399,7 +3460,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>NRG</t>
         </is>
@@ -3505,7 +3566,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ22" s="3" t="inlineStr">
+      <c r="AJ22" s="11" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
@@ -3534,7 +3595,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
@@ -3640,7 +3701,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ23" s="2" t="inlineStr">
+      <c r="AJ23" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -3669,7 +3730,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>HWM</t>
         </is>
@@ -3775,7 +3836,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ24" s="2" t="inlineStr">
+      <c r="AJ24" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -3910,7 +3971,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ25" s="2" t="inlineStr">
+      <c r="AJ25" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -4050,7 +4111,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ26" s="2" t="inlineStr">
+      <c r="AJ26" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -4185,7 +4246,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ27" s="3" t="inlineStr">
+      <c r="AJ27" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -4214,7 +4275,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
@@ -4320,7 +4381,7 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AJ28" s="2" t="inlineStr">
+      <c r="AJ28" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -4349,7 +4410,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>CYBR</t>
         </is>
@@ -4455,7 +4516,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ29" s="2" t="inlineStr">
+      <c r="AJ29" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -4519,7 +4580,7 @@
       <c r="K30" t="n">
         <v>1.66</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="L30" s="14" t="n">
         <v>-1.113107692858614</v>
       </c>
       <c r="M30" t="n">
@@ -4546,7 +4607,7 @@
       <c r="U30" t="n">
         <v>11.11111111111111</v>
       </c>
-      <c r="V30" s="5" t="b">
+      <c r="V30" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W30" t="b">
@@ -4587,7 +4648,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ30" s="3" t="inlineStr">
+      <c r="AJ30" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -4616,7 +4677,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>SFM</t>
         </is>
@@ -4722,7 +4783,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ31" s="3" t="inlineStr">
+      <c r="AJ31" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -4751,7 +4812,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
@@ -4813,7 +4874,7 @@
       <c r="U32" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="V32" s="5" t="b">
+      <c r="V32" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W32" t="b">
@@ -4857,7 +4918,7 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AJ32" s="3" t="inlineStr">
+      <c r="AJ32" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -4886,7 +4947,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
@@ -4992,7 +5053,7 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AJ33" s="3" t="inlineStr">
+      <c r="AJ33" s="11" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -5083,7 +5144,7 @@
       <c r="U34" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="5" t="b">
+      <c r="V34" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W34" t="b">
@@ -5127,7 +5188,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ34" s="2" t="inlineStr">
+      <c r="AJ34" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -5185,7 +5246,7 @@
       <c r="I35" t="n">
         <v>0.77</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="14" t="n">
         <v>-1.055784884813398</v>
       </c>
       <c r="K35" t="n">
@@ -5223,7 +5284,7 @@
       <c r="U35" t="n">
         <v>10</v>
       </c>
-      <c r="V35" s="5" t="b">
+      <c r="V35" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W35" t="b">
@@ -5267,7 +5328,7 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AJ35" s="3" t="inlineStr">
+      <c r="AJ35" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -5331,7 +5392,7 @@
       <c r="K36" t="n">
         <v>1.7</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="L36" s="14" t="n">
         <v>-1.092484537164501</v>
       </c>
       <c r="M36" t="n">
@@ -5402,7 +5463,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ36" s="3" t="inlineStr">
+      <c r="AJ36" s="11" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
@@ -5537,7 +5598,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ37" s="2" t="inlineStr">
+      <c r="AJ37" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -5671,7 +5732,7 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AJ38" s="3" t="inlineStr">
+      <c r="AJ38" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -5700,7 +5761,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>IONQ</t>
         </is>
@@ -5729,13 +5790,13 @@
       <c r="I39" t="n">
         <v>9.15</v>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="J39" s="12" t="n">
         <v>2.276551107257073</v>
       </c>
       <c r="K39" t="n">
         <v>8.43</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="L39" s="12" t="n">
         <v>2.377361408370142</v>
       </c>
       <c r="M39" t="n">
@@ -5806,7 +5867,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ39" s="2" t="inlineStr">
+      <c r="AJ39" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -5946,7 +6007,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ40" s="3" t="inlineStr">
+      <c r="AJ40" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -6081,7 +6142,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ41" s="2" t="inlineStr">
+      <c r="AJ41" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -6218,7 +6279,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ42" s="3" t="inlineStr">
+      <c r="AJ42" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -6247,7 +6308,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
@@ -6282,7 +6343,7 @@
       <c r="K43" t="n">
         <v>1.67</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="L43" s="14" t="n">
         <v>-1.107951903935086</v>
       </c>
       <c r="M43" t="n">
@@ -6353,7 +6414,7 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AJ43" s="3" t="inlineStr">
+      <c r="AJ43" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -6488,7 +6549,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ44" s="2" t="inlineStr">
+      <c r="AJ44" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -6517,7 +6578,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>SPOT</t>
         </is>
@@ -6623,7 +6684,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ45" s="3" t="inlineStr">
+      <c r="AJ45" s="11" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -6758,7 +6819,7 @@
           <t>2025-07-14</t>
         </is>
       </c>
-      <c r="AJ46" s="3" t="inlineStr">
+      <c r="AJ46" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -6849,7 +6910,7 @@
       <c r="U47" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="5" t="b">
+      <c r="V47" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W47" t="b">
@@ -6893,7 +6954,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ47" s="2" t="inlineStr">
+      <c r="AJ47" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -6922,7 +6983,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>FTNT</t>
         </is>
@@ -6984,7 +7045,7 @@
       <c r="U48" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="5" t="b">
+      <c r="V48" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W48" t="b">
@@ -7028,7 +7089,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ48" s="2" t="inlineStr">
+      <c r="AJ48" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -7163,7 +7224,7 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AJ49" s="3" t="inlineStr">
+      <c r="AJ49" s="11" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -7192,7 +7253,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>VRSN</t>
         </is>
@@ -7227,7 +7288,7 @@
       <c r="K50" t="n">
         <v>1.77</v>
       </c>
-      <c r="L50" s="6" t="n">
+      <c r="L50" s="14" t="n">
         <v>-1.056394014699802</v>
       </c>
       <c r="M50" t="n">
@@ -7254,7 +7315,7 @@
       <c r="U50" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="V50" s="5" t="b">
+      <c r="V50" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W50" t="b">
@@ -7298,7 +7359,7 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AJ50" s="2" t="inlineStr">
+      <c r="AJ50" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -7389,7 +7450,7 @@
       <c r="U51" t="n">
         <v>4.444444444444444</v>
       </c>
-      <c r="V51" s="5" t="b">
+      <c r="V51" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W51" t="b">
@@ -7433,7 +7494,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ51" s="2" t="inlineStr">
+      <c r="AJ51" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -7524,7 +7585,7 @@
       <c r="U52" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="5" t="b">
+      <c r="V52" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W52" t="b">
@@ -7568,7 +7629,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ52" s="2" t="inlineStr">
+      <c r="AJ52" s="10" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -7597,7 +7658,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>RBLX</t>
         </is>
@@ -7703,7 +7764,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ53" s="3" t="inlineStr">
+      <c r="AJ53" s="11" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -7838,7 +7899,7 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AJ54" s="2" t="inlineStr">
+      <c r="AJ54" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -7867,7 +7928,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>SRAD</t>
         </is>
@@ -7929,7 +7990,7 @@
       <c r="U55" t="n">
         <v>3.333333333333333</v>
       </c>
-      <c r="V55" s="5" t="b">
+      <c r="V55" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W55" t="b">
@@ -7972,7 +8033,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ55" s="2" t="inlineStr">
+      <c r="AJ55" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -8030,13 +8091,13 @@
       <c r="I56" t="n">
         <v>0.16</v>
       </c>
-      <c r="J56" s="6" t="n">
+      <c r="J56" s="14" t="n">
         <v>-1.298353495214709</v>
       </c>
       <c r="K56" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="L56" s="6" t="n">
+      <c r="L56" s="14" t="n">
         <v>-1.680244474446743</v>
       </c>
       <c r="M56" t="n">
@@ -8063,7 +8124,7 @@
       <c r="U56" t="n">
         <v>2.777777777777778</v>
       </c>
-      <c r="V56" s="5" t="b">
+      <c r="V56" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W56" t="b">
@@ -8107,7 +8168,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ56" s="2" t="inlineStr">
+      <c r="AJ56" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -8136,7 +8197,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>NYAX</t>
         </is>
@@ -8242,7 +8303,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ57" s="2" t="inlineStr">
+      <c r="AJ57" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -8333,7 +8394,7 @@
       <c r="U58" t="n">
         <v>12.77777777777778</v>
       </c>
-      <c r="V58" s="5" t="b">
+      <c r="V58" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W58" t="b">
@@ -8377,7 +8438,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ58" s="2" t="inlineStr">
+      <c r="AJ58" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -8435,13 +8496,13 @@
       <c r="I59" t="n">
         <v>9.85</v>
       </c>
-      <c r="J59" s="4" t="n">
+      <c r="J59" s="12" t="n">
         <v>2.55490852902907</v>
       </c>
       <c r="K59" t="n">
         <v>8.77</v>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="L59" s="12" t="n">
         <v>2.552658231770109</v>
       </c>
       <c r="M59" t="n">
@@ -8512,7 +8573,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ59" s="3" t="inlineStr">
+      <c r="AJ59" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -8647,7 +8708,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ60" s="2" t="inlineStr">
+      <c r="AJ60" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -8711,7 +8772,7 @@
       <c r="K61" t="n">
         <v>9.49</v>
       </c>
-      <c r="L61" s="4" t="n">
+      <c r="L61" s="12" t="n">
         <v>2.923875034264158</v>
       </c>
       <c r="M61" t="n">
@@ -8782,7 +8843,7 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AJ61" s="2" t="inlineStr">
+      <c r="AJ61" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -8917,7 +8978,7 @@
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="AJ62" s="3" t="inlineStr">
+      <c r="AJ62" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -9049,7 +9110,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ63" s="2" t="inlineStr">
+      <c r="AJ63" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -9181,7 +9242,7 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AJ64" s="3" t="inlineStr">
+      <c r="AJ64" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -9245,7 +9306,7 @@
       <c r="K65" t="n">
         <v>8.09</v>
       </c>
-      <c r="L65" s="4" t="n">
+      <c r="L65" s="12" t="n">
         <v>2.202064584970175</v>
       </c>
       <c r="M65" t="n">
@@ -9316,7 +9377,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ65" s="2" t="inlineStr">
+      <c r="AJ65" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -9407,7 +9468,7 @@
       <c r="U66" t="n">
         <v>3.333333333333333</v>
       </c>
-      <c r="V66" s="5" t="b">
+      <c r="V66" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W66" t="b">
@@ -9451,7 +9512,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ66" s="2" t="inlineStr">
+      <c r="AJ66" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -9480,7 +9541,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>LOAR</t>
         </is>
@@ -9586,7 +9647,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ67" s="2" t="inlineStr">
+      <c r="AJ67" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -9721,7 +9782,7 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AJ68" s="3" t="inlineStr">
+      <c r="AJ68" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -9856,7 +9917,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ69" s="3" t="inlineStr">
+      <c r="AJ69" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -9991,7 +10052,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ70" s="2" t="inlineStr">
+      <c r="AJ70" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -10082,7 +10143,7 @@
       <c r="U71" t="n">
         <v>11.66666666666667</v>
       </c>
-      <c r="V71" s="5" t="b">
+      <c r="V71" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W71" t="b">
@@ -10126,7 +10187,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ71" s="2" t="inlineStr">
+      <c r="AJ71" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -10261,7 +10322,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ72" s="3" t="inlineStr">
+      <c r="AJ72" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -10396,7 +10457,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ73" s="3" t="inlineStr">
+      <c r="AJ73" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -10454,13 +10515,13 @@
       <c r="I74" t="n">
         <v>10.11</v>
       </c>
-      <c r="J74" s="4" t="n">
+      <c r="J74" s="12" t="n">
         <v>2.658298428544382</v>
       </c>
       <c r="K74" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="L74" s="4" t="n">
+      <c r="L74" s="12" t="n">
         <v>2.341270885905443</v>
       </c>
       <c r="M74" t="n">
@@ -10531,7 +10592,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ74" s="3" t="inlineStr">
+      <c r="AJ74" s="11" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -10595,7 +10656,7 @@
       <c r="K75" t="n">
         <v>1.8</v>
       </c>
-      <c r="L75" s="6" t="n">
+      <c r="L75" s="14" t="n">
         <v>-1.040926647929216</v>
       </c>
       <c r="M75" t="n">
@@ -10663,7 +10724,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ75" s="3" t="inlineStr">
+      <c r="AJ75" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -10798,7 +10859,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ76" s="3" t="inlineStr">
+      <c r="AJ76" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -10827,7 +10888,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
@@ -10856,13 +10917,13 @@
       <c r="I77" t="n">
         <v>0.19</v>
       </c>
-      <c r="J77" s="6" t="n">
+      <c r="J77" s="14" t="n">
         <v>-1.286423891424481</v>
       </c>
       <c r="K77" t="n">
         <v>0.35</v>
       </c>
-      <c r="L77" s="6" t="n">
+      <c r="L77" s="14" t="n">
         <v>-1.788516041840841</v>
       </c>
       <c r="M77" t="n">
@@ -10889,7 +10950,7 @@
       <c r="U77" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="5" t="b">
+      <c r="V77" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W77" t="b">
@@ -10933,7 +10994,7 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AJ77" s="2" t="inlineStr">
+      <c r="AJ77" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -11068,7 +11129,7 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AJ78" s="2" t="inlineStr">
+      <c r="AJ78" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -11097,7 +11158,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>IHS</t>
         </is>
@@ -11203,7 +11264,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ79" s="3" t="inlineStr">
+      <c r="AJ79" s="11" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -11338,7 +11399,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ80" s="3" t="inlineStr">
+      <c r="AJ80" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -11473,7 +11534,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ81" s="2" t="inlineStr">
+      <c r="AJ81" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -11531,13 +11592,13 @@
       <c r="I82" t="n">
         <v>15.8</v>
       </c>
-      <c r="J82" s="4" t="n">
+      <c r="J82" s="12" t="n">
         <v>4.92094661409104</v>
       </c>
       <c r="K82" t="n">
         <v>10.63</v>
       </c>
-      <c r="L82" s="4" t="n">
+      <c r="L82" s="12" t="n">
         <v>3.5116349715464</v>
       </c>
       <c r="M82" t="n">
@@ -11608,7 +11669,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ82" s="2" t="inlineStr">
+      <c r="AJ82" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -11637,7 +11698,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="12" t="inlineStr">
         <is>
           <t>MRCY</t>
         </is>
@@ -11743,7 +11804,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ83" s="2" t="inlineStr">
+      <c r="AJ83" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -11878,7 +11939,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ84" s="3" t="inlineStr">
+      <c r="AJ84" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -11969,7 +12030,7 @@
       <c r="U85" t="n">
         <v>3.333333333333333</v>
       </c>
-      <c r="V85" s="5" t="b">
+      <c r="V85" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W85" t="b">
@@ -12013,7 +12074,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ85" s="2" t="inlineStr">
+      <c r="AJ85" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -12042,7 +12103,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="12" t="inlineStr">
         <is>
           <t>SGHC</t>
         </is>
@@ -12104,7 +12165,7 @@
       <c r="U86" t="n">
         <v>5</v>
       </c>
-      <c r="V86" s="5" t="b">
+      <c r="V86" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W86" t="b">
@@ -12148,7 +12209,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ86" s="2" t="inlineStr">
+      <c r="AJ86" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -12283,7 +12344,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ87" s="3" t="inlineStr">
+      <c r="AJ87" s="11" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -12415,7 +12476,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ88" s="2" t="inlineStr">
+      <c r="AJ88" s="10" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -12444,7 +12505,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="12" t="inlineStr">
         <is>
           <t>WAY</t>
         </is>
@@ -12544,7 +12605,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ89" s="3" t="inlineStr">
+      <c r="AJ89" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -12679,7 +12740,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ90" s="3" t="inlineStr">
+      <c r="AJ90" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -12770,7 +12831,7 @@
       <c r="U91" t="n">
         <v>14.44444444444444</v>
       </c>
-      <c r="V91" s="5" t="b">
+      <c r="V91" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W91" t="b">
@@ -12814,7 +12875,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ91" s="3" t="inlineStr">
+      <c r="AJ91" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -12949,7 +13010,7 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AJ92" s="2" t="inlineStr">
+      <c r="AJ92" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -13084,7 +13145,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ93" s="3" t="inlineStr">
+      <c r="AJ93" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -13142,13 +13203,13 @@
       <c r="I94" t="n">
         <v>14.25</v>
       </c>
-      <c r="J94" s="4" t="n">
+      <c r="J94" s="12" t="n">
         <v>4.304583751595905</v>
       </c>
       <c r="K94" t="n">
         <v>12.05</v>
       </c>
-      <c r="L94" s="4" t="n">
+      <c r="L94" s="12" t="n">
         <v>4.243756998687439</v>
       </c>
       <c r="M94" t="n">
@@ -13219,7 +13280,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ94" s="2" t="inlineStr">
+      <c r="AJ94" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -13354,7 +13415,7 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AJ95" s="3" t="inlineStr">
+      <c r="AJ95" s="11" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -13491,7 +13552,7 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AJ96" s="3" t="inlineStr">
+      <c r="AJ96" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -13582,7 +13643,7 @@
       <c r="U97" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="5" t="b">
+      <c r="V97" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W97" t="b">
@@ -13626,7 +13687,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ97" s="3" t="inlineStr">
+      <c r="AJ97" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -13655,7 +13716,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="12" t="inlineStr">
         <is>
           <t>ERJ</t>
         </is>
@@ -13761,7 +13822,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ98" s="2" t="inlineStr">
+      <c r="AJ98" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -13896,7 +13957,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ99" s="3" t="inlineStr">
+      <c r="AJ99" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -14033,7 +14094,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ100" s="2" t="inlineStr">
+      <c r="AJ100" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -14168,7 +14229,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ101" s="3" t="inlineStr">
+      <c r="AJ101" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -14297,7 +14358,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ102" s="3" t="inlineStr">
+      <c r="AJ102" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -14432,7 +14493,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ103" s="3" t="inlineStr">
+      <c r="AJ103" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -14567,7 +14628,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ104" s="2" t="inlineStr">
+      <c r="AJ104" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -14702,7 +14763,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ105" s="2" t="inlineStr">
+      <c r="AJ105" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -14793,7 +14854,7 @@
       <c r="U106" t="n">
         <v>6.111111111111111</v>
       </c>
-      <c r="V106" s="5" t="b">
+      <c r="V106" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W106" t="b">
@@ -14837,7 +14898,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ106" s="3" t="inlineStr">
+      <c r="AJ106" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -14866,7 +14927,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="12" t="inlineStr">
         <is>
           <t>VIRT</t>
         </is>
@@ -14928,7 +14989,7 @@
       <c r="U107" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="5" t="b">
+      <c r="V107" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W107" t="b">
@@ -14972,7 +15033,7 @@
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="AJ107" s="3" t="inlineStr">
+      <c r="AJ107" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -15107,7 +15168,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ108" s="3" t="inlineStr">
+      <c r="AJ108" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -15198,7 +15259,7 @@
       <c r="U109" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="5" t="b">
+      <c r="V109" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W109" t="b">
@@ -15242,7 +15303,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ109" s="3" t="inlineStr">
+      <c r="AJ109" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -15377,7 +15438,7 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AJ110" s="2" t="inlineStr">
+      <c r="AJ110" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -15406,7 +15467,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="12" t="inlineStr">
         <is>
           <t>QFIN</t>
         </is>
@@ -15512,7 +15573,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ111" s="3" t="inlineStr">
+      <c r="AJ111" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -15603,7 +15664,7 @@
       <c r="U112" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="5" t="b">
+      <c r="V112" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W112" t="b">
@@ -15647,7 +15708,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ112" s="2" t="inlineStr">
+      <c r="AJ112" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -15676,7 +15737,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="12" t="inlineStr">
         <is>
           <t>NGVC</t>
         </is>
@@ -15782,7 +15843,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ113" s="3" t="inlineStr">
+      <c r="AJ113" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -15811,7 +15872,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="12" t="inlineStr">
         <is>
           <t>LRN</t>
         </is>
@@ -15917,7 +15978,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ114" s="3" t="inlineStr">
+      <c r="AJ114" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -16052,7 +16113,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ115" s="2" t="inlineStr">
+      <c r="AJ115" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -16110,13 +16171,13 @@
       <c r="I116" t="n">
         <v>8.6</v>
       </c>
-      <c r="J116" s="4" t="n">
+      <c r="J116" s="12" t="n">
         <v>2.057841704436219</v>
       </c>
       <c r="K116" t="n">
         <v>7.92</v>
       </c>
-      <c r="L116" s="4" t="n">
+      <c r="L116" s="12" t="n">
         <v>2.114416173270191</v>
       </c>
       <c r="M116" t="n">
@@ -16187,7 +16248,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ116" s="2" t="inlineStr">
+      <c r="AJ116" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -16245,7 +16306,7 @@
       <c r="I117" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="J117" s="4" t="n">
+      <c r="J117" s="12" t="n">
         <v>2.037959031452505</v>
       </c>
       <c r="K117" t="n">
@@ -16322,7 +16383,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ117" s="3" t="inlineStr">
+      <c r="AJ117" s="11" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -16462,7 +16523,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ118" s="2" t="inlineStr">
+      <c r="AJ118" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -16553,7 +16614,7 @@
       <c r="U119" t="n">
         <v>5</v>
       </c>
-      <c r="V119" s="5" t="b">
+      <c r="V119" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W119" t="b">
@@ -16597,7 +16658,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ119" s="2" t="inlineStr">
+      <c r="AJ119" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -16626,7 +16687,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="A120" s="12" t="inlineStr">
         <is>
           <t>SNEX</t>
         </is>
@@ -16688,7 +16749,7 @@
       <c r="U120" t="n">
         <v>8.333333333333332</v>
       </c>
-      <c r="V120" s="5" t="b">
+      <c r="V120" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W120" t="b">
@@ -16732,7 +16793,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ120" s="3" t="inlineStr">
+      <c r="AJ120" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -16823,7 +16884,7 @@
       <c r="U121" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="5" t="b">
+      <c r="V121" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W121" t="b">
@@ -16867,7 +16928,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ121" s="3" t="inlineStr">
+      <c r="AJ121" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -16958,7 +17019,7 @@
       <c r="U122" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="5" t="b">
+      <c r="V122" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W122" t="b">
@@ -17002,7 +17063,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ122" s="2" t="inlineStr">
+      <c r="AJ122" s="10" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -17066,7 +17127,7 @@
       <c r="K123" t="n">
         <v>10.43</v>
       </c>
-      <c r="L123" s="4" t="n">
+      <c r="L123" s="12" t="n">
         <v>3.408519193075831</v>
       </c>
       <c r="M123" t="n">
@@ -17137,7 +17198,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ123" s="3" t="inlineStr">
+      <c r="AJ123" s="11" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -17228,7 +17289,7 @@
       <c r="U124" t="n">
         <v>5.555555555555555</v>
       </c>
-      <c r="V124" s="5" t="b">
+      <c r="V124" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W124" t="b">
@@ -17272,7 +17333,7 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AJ124" s="2" t="inlineStr">
+      <c r="AJ124" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -17407,7 +17468,7 @@
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="AJ125" s="2" t="inlineStr">
+      <c r="AJ125" s="10" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -17498,7 +17559,7 @@
       <c r="U126" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="5" t="b">
+      <c r="V126" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W126" t="b">
@@ -17542,7 +17603,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ126" s="3" t="inlineStr">
+      <c r="AJ126" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -17571,7 +17632,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
+      <c r="A127" s="12" t="inlineStr">
         <is>
           <t>YALA</t>
         </is>
@@ -17677,7 +17738,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ127" s="2" t="inlineStr">
+      <c r="AJ127" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -17768,7 +17829,7 @@
       <c r="U128" t="n">
         <v>9.444444444444443</v>
       </c>
-      <c r="V128" s="5" t="b">
+      <c r="V128" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W128" t="b">
@@ -17812,7 +17873,7 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AJ128" s="3" t="inlineStr">
+      <c r="AJ128" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -17947,7 +18008,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ129" s="2" t="inlineStr">
+      <c r="AJ129" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -17976,7 +18037,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr">
+      <c r="A130" s="12" t="inlineStr">
         <is>
           <t>SYBT</t>
         </is>
@@ -18082,7 +18143,7 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AJ130" s="3" t="inlineStr">
+      <c r="AJ130" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -18111,7 +18172,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
+      <c r="A131" s="12" t="inlineStr">
         <is>
           <t>DRVN</t>
         </is>
@@ -18217,7 +18278,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ131" s="2" t="inlineStr">
+      <c r="AJ131" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -18352,7 +18413,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ132" s="3" t="inlineStr">
+      <c r="AJ132" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -18443,7 +18504,7 @@
       <c r="U133" t="n">
         <v>0.5555555555555555</v>
       </c>
-      <c r="V133" s="5" t="b">
+      <c r="V133" s="13" t="b">
         <v>1</v>
       </c>
       <c r="W133" t="b">
@@ -18487,7 +18548,7 @@
           <t>2025-07-14</t>
         </is>
       </c>
-      <c r="AJ133" s="3" t="inlineStr">
+      <c r="AJ133" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -18622,7 +18683,7 @@
           <t>2025-07-17</t>
         </is>
       </c>
-      <c r="AJ134" s="2" t="inlineStr">
+      <c r="AJ134" s="10" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>

--- a/Result/24-05-25/NASDAQstock_24-05-25period252RS90.xlsx
+++ b/Result/24-05-25/NASDAQstock_24-05-25period252RS90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/24-05-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEACA426-85F4-3049-A2FB-FEC52B168DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D766EDE5-9435-5B47-A93C-82850D387F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -959,7 +959,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -988,6 +988,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFA500"/>
         <bgColor rgb="FFFFA500"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1027,7 +1033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1040,6 +1046,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2227,7 +2234,7 @@
       </c>
     </row>
     <row r="8" spans="1:42">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="10" t="s">
         <v>67</v>
       </c>
       <c r="B8">
@@ -3977,7 +3984,7 @@
       </c>
     </row>
     <row r="22" spans="1:42">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="10" t="s">
         <v>105</v>
       </c>
       <c r="B22">
@@ -5352,7 +5359,7 @@
       </c>
     </row>
     <row r="33" spans="1:42">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="10" t="s">
         <v>130</v>
       </c>
       <c r="B33">
@@ -7855,7 +7862,7 @@
       </c>
     </row>
     <row r="53" spans="1:42">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="10" t="s">
         <v>173</v>
       </c>
       <c r="B53">

--- a/Result/24-05-25/NASDAQstock_24-05-25period252RS90.xlsx
+++ b/Result/24-05-25/NASDAQstock_24-05-25period252RS90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/24-05-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D766EDE5-9435-5B47-A93C-82850D387F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E509CB5-C3D4-8A4C-893A-FE68E90772DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
